--- a/artfynd/A 9048-2024 artfynd.xlsx
+++ b/artfynd/A 9048-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1988,250 +1988,6 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>114833037</v>
-      </c>
-      <c r="B12" t="n">
-        <v>104698</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>340</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Ryl</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Chimaphila umbellata</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Östra Sandar. Åhus kyrka, 3,0 km NNO, Sk</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>456716</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6200748</v>
-      </c>
-      <c r="S12" t="n">
-        <v>10</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Kristianstad</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Åhus</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>M-Kri-0650</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2024-02-24</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2024-02-24</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Charlotte Wigermo</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Charlotte Wigermo</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>114832415</v>
-      </c>
-      <c r="B13" t="n">
-        <v>104698</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>340</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Ryl</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Chimaphila umbellata</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Östra Sandar. Åhus kyrka, 2,8 km NNO, Sk</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>456848</v>
-      </c>
-      <c r="R13" t="n">
-        <v>6200502</v>
-      </c>
-      <c r="S13" t="n">
-        <v>10</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Kristianstad</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Åhus</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>M-Kri-0685</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2024-02-24</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2024-02-24</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Charlotte Wigermo</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Charlotte Wigermo</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9048-2024 artfynd.xlsx
+++ b/artfynd/A 9048-2024 artfynd.xlsx
@@ -804,12 +804,7 @@
         <v>64121998</v>
       </c>
       <c r="B3" t="n">
-        <v>96362</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98614</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456822.266118614</v>
+        <v>456822</v>
       </c>
       <c r="R3" t="n">
-        <v>6200654.191355565</v>
+        <v>6200654</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -874,19 +869,9 @@
           <t>1994-06-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1994-06-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -935,12 +920,7 @@
         <v>64122002</v>
       </c>
       <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100768</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -972,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456722.3896999954</v>
+        <v>456722</v>
       </c>
       <c r="R4" t="n">
-        <v>6200652.951753248</v>
+        <v>6200653</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -1005,19 +985,9 @@
           <t>1994-06-24</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1994-06-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1066,12 +1036,7 @@
         <v>64122005</v>
       </c>
       <c r="B5" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105630</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456722.3896999954</v>
+        <v>456722</v>
       </c>
       <c r="R5" t="n">
-        <v>6200652.951753248</v>
+        <v>6200653</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1136,19 +1101,9 @@
           <t>1994-06-24</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1994-06-24</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1197,12 +1152,7 @@
         <v>64121999</v>
       </c>
       <c r="B6" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98563</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456822.266118614</v>
+        <v>456822</v>
       </c>
       <c r="R6" t="n">
-        <v>6200654.191355565</v>
+        <v>6200654</v>
       </c>
       <c r="S6" t="n">
         <v>100</v>
@@ -1267,19 +1217,9 @@
           <t>1994-06-24</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>1994-06-24</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1328,12 +1268,7 @@
         <v>64122003</v>
       </c>
       <c r="B7" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98563</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456722.3896999954</v>
+        <v>456722</v>
       </c>
       <c r="R7" t="n">
-        <v>6200652.951753248</v>
+        <v>6200653</v>
       </c>
       <c r="S7" t="n">
         <v>100</v>
@@ -1398,19 +1333,9 @@
           <t>1994-06-24</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>1994-06-24</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1459,12 +1384,7 @@
         <v>64122004</v>
       </c>
       <c r="B8" t="n">
-        <v>103226</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105591</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1496,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456722.3896999954</v>
+        <v>456722</v>
       </c>
       <c r="R8" t="n">
-        <v>6200652.951753248</v>
+        <v>6200653</v>
       </c>
       <c r="S8" t="n">
         <v>100</v>
@@ -1529,19 +1449,9 @@
           <t>1994-06-24</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>1994-06-24</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">

--- a/artfynd/A 9048-2024 artfynd.xlsx
+++ b/artfynd/A 9048-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>64121998</v>
       </c>
       <c r="B3" t="n">
-        <v>98614</v>
+        <v>98617</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>64122002</v>
       </c>
       <c r="B4" t="n">
-        <v>100768</v>
+        <v>100773</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>64122005</v>
       </c>
       <c r="B5" t="n">
-        <v>105630</v>
+        <v>105642</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>64121999</v>
       </c>
       <c r="B6" t="n">
-        <v>98563</v>
+        <v>98566</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>64122003</v>
       </c>
       <c r="B7" t="n">
-        <v>98563</v>
+        <v>98566</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>64122004</v>
       </c>
       <c r="B8" t="n">
-        <v>105591</v>
+        <v>105603</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 9048-2024 artfynd.xlsx
+++ b/artfynd/A 9048-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>64121998</v>
       </c>
       <c r="B3" t="n">
-        <v>98617</v>
+        <v>98620</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>64122002</v>
       </c>
       <c r="B4" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>64122005</v>
       </c>
       <c r="B5" t="n">
-        <v>105642</v>
+        <v>105651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>64121999</v>
       </c>
       <c r="B6" t="n">
-        <v>98566</v>
+        <v>98569</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>64122003</v>
       </c>
       <c r="B7" t="n">
-        <v>98566</v>
+        <v>98569</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>64122004</v>
       </c>
       <c r="B8" t="n">
-        <v>105603</v>
+        <v>105612</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 9048-2024 artfynd.xlsx
+++ b/artfynd/A 9048-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>64121998</v>
       </c>
       <c r="B3" t="n">
-        <v>98620</v>
+        <v>98621</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>64122002</v>
       </c>
       <c r="B4" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>64122005</v>
       </c>
       <c r="B5" t="n">
-        <v>105651</v>
+        <v>105654</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>64121999</v>
       </c>
       <c r="B6" t="n">
-        <v>98569</v>
+        <v>98570</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>64122003</v>
       </c>
       <c r="B7" t="n">
-        <v>98569</v>
+        <v>98570</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>64122004</v>
       </c>
       <c r="B8" t="n">
-        <v>105612</v>
+        <v>105615</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 9048-2024 artfynd.xlsx
+++ b/artfynd/A 9048-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>64121998</v>
       </c>
       <c r="B3" t="n">
-        <v>98621</v>
+        <v>98648</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>64122002</v>
       </c>
       <c r="B4" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>64122005</v>
       </c>
       <c r="B5" t="n">
-        <v>105654</v>
+        <v>105682</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>64121999</v>
       </c>
       <c r="B6" t="n">
-        <v>98570</v>
+        <v>98597</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>64122003</v>
       </c>
       <c r="B7" t="n">
-        <v>98570</v>
+        <v>98597</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>64122004</v>
       </c>
       <c r="B8" t="n">
-        <v>105615</v>
+        <v>105643</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 9048-2024 artfynd.xlsx
+++ b/artfynd/A 9048-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>64121998</v>
       </c>
       <c r="B3" t="n">
-        <v>98648</v>
+        <v>98654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>64122002</v>
       </c>
       <c r="B4" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>64122005</v>
       </c>
       <c r="B5" t="n">
-        <v>105682</v>
+        <v>105688</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>64121999</v>
       </c>
       <c r="B6" t="n">
-        <v>98597</v>
+        <v>98603</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>64122003</v>
       </c>
       <c r="B7" t="n">
-        <v>98597</v>
+        <v>98603</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>64122004</v>
       </c>
       <c r="B8" t="n">
-        <v>105643</v>
+        <v>105649</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 9048-2024 artfynd.xlsx
+++ b/artfynd/A 9048-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>64121998</v>
       </c>
       <c r="B3" t="n">
-        <v>98654</v>
+        <v>98661</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>64122002</v>
       </c>
       <c r="B4" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>64122005</v>
       </c>
       <c r="B5" t="n">
-        <v>105688</v>
+        <v>105695</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>64121999</v>
       </c>
       <c r="B6" t="n">
-        <v>98603</v>
+        <v>98610</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>64122003</v>
       </c>
       <c r="B7" t="n">
-        <v>98603</v>
+        <v>98610</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>64122004</v>
       </c>
       <c r="B8" t="n">
-        <v>105649</v>
+        <v>105656</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 9048-2024 artfynd.xlsx
+++ b/artfynd/A 9048-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>64121998</v>
       </c>
       <c r="B3" t="n">
-        <v>98661</v>
+        <v>98665</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>64122002</v>
       </c>
       <c r="B4" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>64122005</v>
       </c>
       <c r="B5" t="n">
-        <v>105695</v>
+        <v>105699</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>64121999</v>
       </c>
       <c r="B6" t="n">
-        <v>98610</v>
+        <v>98614</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>64122003</v>
       </c>
       <c r="B7" t="n">
-        <v>98610</v>
+        <v>98614</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>64122004</v>
       </c>
       <c r="B8" t="n">
-        <v>105656</v>
+        <v>105660</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 9048-2024 artfynd.xlsx
+++ b/artfynd/A 9048-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>64121998</v>
       </c>
       <c r="B3" t="n">
-        <v>98665</v>
+        <v>98672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>64122002</v>
       </c>
       <c r="B4" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>64122005</v>
       </c>
       <c r="B5" t="n">
-        <v>105699</v>
+        <v>105706</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>64121999</v>
       </c>
       <c r="B6" t="n">
-        <v>98614</v>
+        <v>98621</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>64122003</v>
       </c>
       <c r="B7" t="n">
-        <v>98614</v>
+        <v>98621</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>64122004</v>
       </c>
       <c r="B8" t="n">
-        <v>105660</v>
+        <v>105667</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 9048-2024 artfynd.xlsx
+++ b/artfynd/A 9048-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>64121998</v>
       </c>
       <c r="B3" t="n">
-        <v>98675</v>
+        <v>98680</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>64122002</v>
       </c>
       <c r="B4" t="n">
-        <v>100834</v>
+        <v>100839</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>64122005</v>
       </c>
       <c r="B5" t="n">
-        <v>105709</v>
+        <v>105714</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>64121999</v>
       </c>
       <c r="B6" t="n">
-        <v>98624</v>
+        <v>98629</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>64122003</v>
       </c>
       <c r="B7" t="n">
-        <v>98624</v>
+        <v>98629</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>64122004</v>
       </c>
       <c r="B8" t="n">
-        <v>105670</v>
+        <v>105675</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 9048-2024 artfynd.xlsx
+++ b/artfynd/A 9048-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>64121998</v>
       </c>
       <c r="B3" t="n">
-        <v>98680</v>
+        <v>98688</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>64122002</v>
       </c>
       <c r="B4" t="n">
-        <v>100839</v>
+        <v>100847</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>64122005</v>
       </c>
       <c r="B5" t="n">
-        <v>105714</v>
+        <v>105722</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>64121999</v>
       </c>
       <c r="B6" t="n">
-        <v>98629</v>
+        <v>98637</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>64122003</v>
       </c>
       <c r="B7" t="n">
-        <v>98629</v>
+        <v>98637</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>64122004</v>
       </c>
       <c r="B8" t="n">
-        <v>105675</v>
+        <v>105683</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 9048-2024 artfynd.xlsx
+++ b/artfynd/A 9048-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>64121998</v>
       </c>
       <c r="B3" t="n">
-        <v>98688</v>
+        <v>98698</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>64122002</v>
       </c>
       <c r="B4" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>64122005</v>
       </c>
       <c r="B5" t="n">
-        <v>105722</v>
+        <v>105732</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>64121999</v>
       </c>
       <c r="B6" t="n">
-        <v>98637</v>
+        <v>98647</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>64122003</v>
       </c>
       <c r="B7" t="n">
-        <v>98637</v>
+        <v>98647</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>64122004</v>
       </c>
       <c r="B8" t="n">
-        <v>105683</v>
+        <v>105693</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 9048-2024 artfynd.xlsx
+++ b/artfynd/A 9048-2024 artfynd.xlsx
@@ -1632,12 +1632,7 @@
         <v>76327073</v>
       </c>
       <c r="B10" t="n">
-        <v>103226</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>105751</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,10 +1676,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456847.6715096359</v>
+        <v>456848</v>
       </c>
       <c r="R10" t="n">
-        <v>6200501.655386933</v>
+        <v>6200502</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1719,19 +1714,9 @@
           <t>2019-03-09</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2019-03-09</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1766,12 +1751,7 @@
         <v>137533</v>
       </c>
       <c r="B11" t="n">
-        <v>103226</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>105751</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1814,10 +1794,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456716.0508849474</v>
+        <v>456716</v>
       </c>
       <c r="R11" t="n">
-        <v>6200748.1889241</v>
+        <v>6200748</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1852,19 +1832,9 @@
           <t>2013-04-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2013-04-01</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">

--- a/artfynd/A 9048-2024 artfynd.xlsx
+++ b/artfynd/A 9048-2024 artfynd.xlsx
@@ -1632,7 +1632,7 @@
         <v>76327073</v>
       </c>
       <c r="B10" t="n">
-        <v>105751</v>
+        <v>105754</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>137533</v>
       </c>
       <c r="B11" t="n">
-        <v>105751</v>
+        <v>105754</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 9048-2024 artfynd.xlsx
+++ b/artfynd/A 9048-2024 artfynd.xlsx
@@ -1632,7 +1632,7 @@
         <v>76327073</v>
       </c>
       <c r="B10" t="n">
-        <v>105754</v>
+        <v>105783</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>137533</v>
       </c>
       <c r="B11" t="n">
-        <v>105754</v>
+        <v>105783</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 9048-2024 artfynd.xlsx
+++ b/artfynd/A 9048-2024 artfynd.xlsx
@@ -1632,7 +1632,7 @@
         <v>76327073</v>
       </c>
       <c r="B10" t="n">
-        <v>105783</v>
+        <v>105795</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>137533</v>
       </c>
       <c r="B11" t="n">
-        <v>105783</v>
+        <v>105795</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 9048-2024 artfynd.xlsx
+++ b/artfynd/A 9048-2024 artfynd.xlsx
@@ -1632,7 +1632,7 @@
         <v>76327073</v>
       </c>
       <c r="B10" t="n">
-        <v>105795</v>
+        <v>105796</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>137533</v>
       </c>
       <c r="B11" t="n">
-        <v>105795</v>
+        <v>105796</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 9048-2024 artfynd.xlsx
+++ b/artfynd/A 9048-2024 artfynd.xlsx
@@ -1632,7 +1632,7 @@
         <v>76327073</v>
       </c>
       <c r="B10" t="n">
-        <v>105796</v>
+        <v>105801</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>137533</v>
       </c>
       <c r="B11" t="n">
-        <v>105796</v>
+        <v>105801</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 9048-2024 artfynd.xlsx
+++ b/artfynd/A 9048-2024 artfynd.xlsx
@@ -1632,7 +1632,7 @@
         <v>76327073</v>
       </c>
       <c r="B10" t="n">
-        <v>105801</v>
+        <v>105805</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>137533</v>
       </c>
       <c r="B11" t="n">
-        <v>105801</v>
+        <v>105805</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 9048-2024 artfynd.xlsx
+++ b/artfynd/A 9048-2024 artfynd.xlsx
@@ -1632,7 +1632,7 @@
         <v>76327073</v>
       </c>
       <c r="B10" t="n">
-        <v>105805</v>
+        <v>105807</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>137533</v>
       </c>
       <c r="B11" t="n">
-        <v>105805</v>
+        <v>105807</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 9048-2024 artfynd.xlsx
+++ b/artfynd/A 9048-2024 artfynd.xlsx
@@ -1632,7 +1632,7 @@
         <v>76327073</v>
       </c>
       <c r="B10" t="n">
-        <v>105807</v>
+        <v>105817</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>137533</v>
       </c>
       <c r="B11" t="n">
-        <v>105807</v>
+        <v>105817</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 9048-2024 artfynd.xlsx
+++ b/artfynd/A 9048-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>64121998</v>
       </c>
       <c r="B3" t="n">
-        <v>99050</v>
+        <v>99052</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>900044</v>
       </c>
       <c r="B9" t="n">
-        <v>110270</v>
+        <v>110286</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 9048-2024 artfynd.xlsx
+++ b/artfynd/A 9048-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>64121998</v>
       </c>
       <c r="B3" t="n">
-        <v>99052</v>
+        <v>99053</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>900044</v>
       </c>
       <c r="B9" t="n">
-        <v>110286</v>
+        <v>110287</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 9048-2024 artfynd.xlsx
+++ b/artfynd/A 9048-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>64121998</v>
       </c>
       <c r="B3" t="n">
-        <v>99053</v>
+        <v>99054</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>900044</v>
       </c>
       <c r="B9" t="n">
-        <v>110287</v>
+        <v>110288</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 9048-2024 artfynd.xlsx
+++ b/artfynd/A 9048-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>64121998</v>
       </c>
       <c r="B3" t="n">
-        <v>99054</v>
+        <v>99057</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 9048-2024 artfynd.xlsx
+++ b/artfynd/A 9048-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>64121998</v>
       </c>
       <c r="B3" t="n">
-        <v>99057</v>
+        <v>99058</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 9048-2024 artfynd.xlsx
+++ b/artfynd/A 9048-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>64121998</v>
       </c>
       <c r="B3" t="n">
-        <v>99058</v>
+        <v>99064</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 9048-2024 artfynd.xlsx
+++ b/artfynd/A 9048-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>64121998</v>
       </c>
       <c r="B3" t="n">
-        <v>99064</v>
+        <v>99065</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 9048-2024 artfynd.xlsx
+++ b/artfynd/A 9048-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>64121998</v>
       </c>
       <c r="B3" t="n">
-        <v>99065</v>
+        <v>99066</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 9048-2024 artfynd.xlsx
+++ b/artfynd/A 9048-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>64121998</v>
       </c>
       <c r="B3" t="n">
-        <v>99066</v>
+        <v>99069</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 9048-2024 artfynd.xlsx
+++ b/artfynd/A 9048-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>55928411</v>
+        <v>117390</v>
       </c>
       <c r="B2" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106204</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221725</v>
+        <v>340</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Horna fure, Sk</t>
+          <t>Östra Sandar. Åhus kyrka, 3,0 km NNO, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>456910.641217498</v>
+        <v>456716</v>
       </c>
       <c r="R2" t="n">
-        <v>6200683.540430702</v>
+        <v>6200748</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,24 +738,24 @@
           <t>Åhus</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>M-Kri-0650</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-06-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1994-06-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-06-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1994-06-24</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>3E0b3313, 3E0b3314, 3E0b3513. Finns.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,66 +769,81 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>gles, sandig tallskog</t>
+          <t>gles tallskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Skåne Floraväktarna</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kjell-arne Olsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Åke Svensson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>64121998</v>
+        <v>133310</v>
       </c>
       <c r="B3" t="n">
-        <v>99170</v>
+        <v>106204</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219865</v>
+        <v>340</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Johannesnycklar</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Orchis militaris</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1,6 km O Skogstorpet, Sk</t>
+          <t>Östra Sandar. Åhus kyrka, 2,8 km NNO, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456822</v>
+        <v>456848</v>
       </c>
       <c r="R3" t="n">
-        <v>6200654</v>
+        <v>6200502</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,19 +865,24 @@
           <t>Åhus</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>M-Kri-0685</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1994-06-24</t>
+          <t>2009-08-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1994-06-24</t>
+          <t>2009-08-10</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Orchis militaris/3E0b3315/Åhus s:n/SBi/ /Sven Birkedal,Åhus</t>
+          <t>100 ex. på 3E0b3114, 28 ex. på 3E0b3115.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,59 +896,54 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>glänta, 1 blommande ex</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>SkFlora    232051</t>
+          <t>gles tallskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>Skåne Floraväktarna</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sven Birkedal</t>
+          <t>Kjell-arne Olsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Skånes Flora (1989-2006)</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>64122002</v>
+        <v>64122004</v>
       </c>
       <c r="B4" t="n">
-        <v>100857</v>
+        <v>106204</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>340</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) W. P. C. Barton</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -992,7 +993,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis/3E0b3314/Åhus s:n/SBi/ /Sven Birkedal,Åhus</t>
+          <t>Chimaphila umbellata/3E0b3314/Åhus s:n/SBi/ /Sven Birkedal,Åhus</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1012,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>SkFlora    232055</t>
+          <t>SkFlora    232057</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1033,48 +1034,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>64122005</v>
+        <v>900044</v>
       </c>
       <c r="B5" t="n">
-        <v>105732</v>
+        <v>110471</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>1947</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Glappmaskros</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Taraxacum discretum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>H. Øllg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1,5 km O Skogstorpet, Sk</t>
+          <t>Östra Sandar. Åhus kyrka, 3,0 km NNO, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456722</v>
+        <v>456922</v>
       </c>
       <c r="R5" t="n">
-        <v>6200653</v>
+        <v>6200655</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,19 +1097,24 @@
           <t>Åhus</t>
         </is>
       </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>M-Kri-0986</t>
+        </is>
+      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1994-06-24</t>
+          <t>1995-06-05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1994-06-24</t>
+          <t>1995-06-05</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha/3E0b3314/Åhus s:n/SBi/ /Sven Birkedal,Åhus</t>
+          <t>3E0b3316</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,28 +1128,24 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>gles tallskog</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>SkFlora    232058</t>
-        </is>
-      </c>
+          <t>i gles tallskog</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr"/>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>Skåne Floraväktarna</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sven Birkedal</t>
+          <t>Åke Svensson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Skånes Flora (1989-2006)</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1154,7 @@
         <v>64121999</v>
       </c>
       <c r="B6" t="n">
-        <v>98647</v>
+        <v>99096</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1270,7 @@
         <v>64122003</v>
       </c>
       <c r="B7" t="n">
-        <v>98647</v>
+        <v>99096</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1381,45 +1383,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>64122004</v>
+        <v>64121998</v>
       </c>
       <c r="B8" t="n">
-        <v>105693</v>
+        <v>99225</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>340</v>
+        <v>219865</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Johannesnycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Orchis militaris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1,5 km O Skogstorpet, Sk</t>
+          <t>1,6 km O Skogstorpet, Sk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456722</v>
+        <v>456822</v>
       </c>
       <c r="R8" t="n">
-        <v>6200653</v>
+        <v>6200654</v>
       </c>
       <c r="S8" t="n">
         <v>100</v>
@@ -1456,7 +1458,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata/3E0b3314/Åhus s:n/SBi/ /Sven Birkedal,Åhus</t>
+          <t>Orchis militaris/3E0b3315/Åhus s:n/SBi/ /Sven Birkedal,Åhus</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,12 +1472,12 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>gles tallskog</t>
+          <t>glänta, 1 blommande ex</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>SkFlora    232057</t>
+          <t>SkFlora    232051</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1497,48 +1499,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>900044</v>
+        <v>64122005</v>
       </c>
       <c r="B9" t="n">
-        <v>110415</v>
+        <v>106243</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1947</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Glappmaskros</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Taraxacum discretum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>H. Øllg.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Östra Sandar. Åhus kyrka, 3,0 km NNO, Sk</t>
+          <t>1,5 km O Skogstorpet, Sk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456922</v>
+        <v>456722</v>
       </c>
       <c r="R9" t="n">
-        <v>6200655</v>
+        <v>6200653</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1560,24 +1562,19 @@
           <t>Åhus</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>M-Kri-0986</t>
-        </is>
-      </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>1995-06-05</t>
+          <t>1994-06-24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1995-06-05</t>
+          <t>1994-06-24</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>3E0b3316</t>
+          <t>Pyrola chlorantha/3E0b3314/Åhus s:n/SBi/ /Sven Birkedal,Åhus</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,83 +1588,84 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>i gles tallskog</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr"/>
+          <t>gles tallskog</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>SkFlora    232058</t>
+        </is>
+      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Skåne Floraväktarna</t>
+          <t>Stefan Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Åke Svensson</t>
+          <t>Sven Birkedal</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>76327073</v>
+        <v>55928411</v>
       </c>
       <c r="B10" t="n">
-        <v>105817</v>
+        <v>106229</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>340</v>
+        <v>221725</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>145</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Östra Sandar. Åhus kyrka, 2,8 km NNO, Sk</t>
+          <t>Horna fure, Sk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456848</v>
+        <v>456911</v>
       </c>
       <c r="R10" t="n">
-        <v>6200502</v>
+        <v>6200684</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1689,19 +1687,14 @@
           <t>Åhus</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>M-Kri-0685</t>
-        </is>
-      </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2019-03-09</t>
+          <t>2015-06-06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2019-03-09</t>
+          <t>2015-06-06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,9 +1703,13 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>gles, sandig tallskog</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1722,70 +1719,63 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Kjell-arne Olsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137533</v>
+        <v>129939132</v>
       </c>
       <c r="B11" t="n">
-        <v>105817</v>
+        <v>107516</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>340</v>
+        <v>221849</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Östra Sandar. Åhus kyrka, 3,0 km NNO, Sk</t>
+          <t>Östra Sand, Sk</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456716</v>
+        <v>456714</v>
       </c>
       <c r="R11" t="n">
-        <v>6200748</v>
+        <v>6200548</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1807,24 +1797,14 @@
           <t>Åhus</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>M-Kri-0650</t>
-        </is>
-      </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2013-04-01</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2013-04-01</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>77 ex. på 6203581, 1406408. 96 ex. på 3328, 6517.53 ex. på 3293, 6212.</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1833,23 +1813,141 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Kalkpåverkad sandtallskog</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Örjan Fritz</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>64122002</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>1,5 km O Skogstorpet, Sk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>456722</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6200653</v>
+      </c>
+      <c r="S12" t="n">
+        <v>100</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Åhus</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>1994-06-24</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>1994-06-24</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis/3E0b3314/Åhus s:n/SBi/ /Sven Birkedal,Åhus</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>gles tallskog</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>SkFlora    232055</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Sven Birkedal</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 9048-2024 artfynd.xlsx
+++ b/artfynd/A 9048-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117390</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -915,6 +925,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133310</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1031,6 +1046,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64122004</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1148,6 +1168,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/900044</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1264,6 +1289,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64121999</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1380,6 +1410,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64122003</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1496,6 +1531,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64121998</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1612,6 +1652,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64122005</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1723,6 +1768,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55928411</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1834,6 +1884,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129939132</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1950,8 +2005,26 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64122002</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>